--- a/site/Active-Directory-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Users</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KS1WZAG235WZRWNZWA0VQWWG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS1WZAG235WZRWNZWA0VQWWG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>User Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY4B8Q3SJRP2S701X7</t>
+          <t>h_01KS1XJAK60HDCRMT3QHSACBXB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCACEEY4B8Q3SJRP2S701X7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS1XJAK60HDCRMT3QHSACBXB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Provisioning Settings</t>
+          <t>Group Correlation Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01K35A8BW0AFVC2DSAZHQQXN72</t>
+          <t>h_01KS1XM5VDPY6ZB04F79JDEZYW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K35A8BW0AFVC2DSAZHQQXN72</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS1XM5VDPY6ZB04F79JDEZYW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>User Creation Settings</t>
+          <t>Manage Users</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>User Updation Settings</t>
+          <t>User Provisioning Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
+          <t>h_01K35A8BW0AFVC2DSAZHQQXN72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K35A8BW0AFVC2DSAZHQQXN72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>User Deactivation Settings</t>
+          <t>User Creation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJCB6WM1RKBRB9K1SK6204X9</t>
+          <t>h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCB6WM1RKBRB9K1SK6204X9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJC5XNEZ1QQWAQ5E4JSNA7A6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Future Hire Settings</t>
+          <t>User Updation Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMD70678KJ57FAQ7W2FBCAZY</t>
+          <t>h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KMD70678KJ57FAQ7W2FBCAZY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCACEEYVYVM0GVWWTAJ1AQ7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Inactive User Discovery Settings</t>
+          <t>User Deactivation Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMD73YA4D0AECSBBRHMJY2N7</t>
+          <t>h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KMD73YA4D0AECSBBRHMJY2N7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCB6WM1RKBRB9K1SK6204X9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Inactive User Management Settings</t>
+          <t>Inactive User Discovery Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMD7419Z4SKADMAFVDTE4YTE</t>
+          <t>h_01KMD73YA4D0AECSBBRHMJY2N7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KMD7419Z4SKADMAFVDTE4YTE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KMD73YA4D0AECSBBRHMJY2N7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>User Deletion Settings</t>
+          <t>Inactive User Management Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMD7445RKSVRCMZV5F9GWGMW</t>
+          <t>h_01KMD7419Z4SKADMAFVDTE4YTE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KMD7445RKSVRCMZV5F9GWGMW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KMD7419Z4SKADMAFVDTE4YTE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ticket Management Settings</t>
+          <t>User Deletion Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KNPHHJVR3BATK66ESHZ58ADW</t>
+          <t>h_01KMD7445RKSVRCMZV5F9GWGMW</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KNPHHJVR3BATK66ESHZ58ADW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KMD7445RKSVRCMZV5F9GWGMW</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Group Management</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,252 +1067,494 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
+          <t>h_01KS2B0YT3JFKV6TGG3BC276ZE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS2B0YT3JFKV6TGG3BC276ZE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Group Management Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>h_01KJCACEEY4B8Q3SJRP2S701X7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCACEEY4B8Q3SJRP2S701X7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Security Group Management Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>h_01KS2B3R1DEG54292NAEH7CYGC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS2B3R1DEG54292NAEH7CYGC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Distribution List Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KNRGEWH3ZRS0M6A63W6WBTX4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KNRGEWH3ZRS0M6A63W6WBTX4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Ticket Reassignment</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KNPGAX4E2ZC0M4P7QQFSTVF4</t>
+          <t>h_01KS2B3R1DWH19000FVK3X6YND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KNPGAX4E2ZC0M4P7QQFSTVF4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS2B3R1DWH19000FVK3X6YND</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OU Assignment Rules</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>h_01KS2BNZCNCXHQG1058VFC5TAZ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS2BNZCNCXHQG1058VFC5TAZ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Group Assignment Rules</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KJYJR534NQZYWAK7H0X9NA4C</t>
+          <t>h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJYJR534NQZYWAK7H0X9NA4C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJSG3B4TWY4Y0YHA7JYH681N</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJCACEEY59F57BDZB9P806BK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJPK5XFJJ4APFAYTF6WSS6A2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KS28G20Z3XWZ0H8AZCKS2V1C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS28G20Z3XWZ0H8AZCKS2V1C</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KS28NSW9MXQDF4MF4A6TB150</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS28NSW9MXQDF4MF4A6TB150</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Failure Execution</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KS28XQ89AZMKZWX6HBWTRNBF</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS28XQ89AZMKZWX6HBWTRNBF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Skipping Execution</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KS2910RA2DDQNNK2JPSM5R8R</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS2910RA2DDQNNK2JPSM5R8R</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KS295BS3D6SVGV5N43A6RK6T</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KS295BS3D6SVGV5N43A6RK6T</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01KNPGAX4E2ZC0M4P7QQFSTVF4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KNPGAX4E2ZC0M4P7QQFSTVF4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OU Assignment Rules</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Group Assignment Rules</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KJYJR534NQZYWAK7H0X9NA4C</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJYJR534NQZYWAK7H0X9NA4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KJQBZ2W357JNQX1FM9HFDPE0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
